--- a/public/templates/Kontrak_Manajemen.xlsx
+++ b/public/templates/Kontrak_Manajemen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghifa\Documents\admin-dashboard\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C63FA22-905D-422C-B480-B56A4B6D1F7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198351AE-D80B-479C-8DA7-668969751F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5BFAE523-3C32-487F-867A-BFB50E6068E4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>SASARAN STRATEGIS</t>
   </si>
@@ -81,13 +81,7 @@
     <t>S (Support)        :     Pendukung</t>
   </si>
   <si>
-    <t>IIP ARIEF BUDIMAN</t>
-  </si>
-  <si>
     <t>Direktur Utama</t>
-  </si>
-  <si>
-    <t>GESRANG TARIGAN</t>
   </si>
   <si>
     <t>Plt. Direktur Keungan &amp; SDM</t>
@@ -233,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -278,6 +272,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -909,63 +906,69 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>13</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>12</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>14</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B43" s="8" t="s">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B43" s="8"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B44" s="9" t="s">
         <v>15</v>
-      </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-      <c r="I43" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="9"/>
-      <c r="K43" s="9"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B44" s="9" t="s">
-        <v>16</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E44" s="9"/>
       <c r="F44" s="9"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
       <c r="I44" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J44" s="9"/>
       <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
+    <mergeCell ref="D38:H38"/>
     <mergeCell ref="A34:C34"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A36:C36"/>
@@ -981,10 +984,10 @@
     <mergeCell ref="H9:H11"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="I43:K43"/>
-    <mergeCell ref="I44:K44"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="D44:H44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/public/templates/Kontrak_Manajemen.xlsx
+++ b/public/templates/Kontrak_Manajemen.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ghifa\Documents\admin-dashboard\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198351AE-D80B-479C-8DA7-668969751F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE393CA5-451A-4686-BA04-01C3819C3223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5BFAE523-3C32-487F-867A-BFB50E6068E4}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>SASARAN STRATEGIS</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>Direktur Operasi</t>
+  </si>
+  <si>
+    <t>Tempat, Tanggal</t>
   </si>
 </sst>
 </file>
@@ -246,35 +249,35 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -782,36 +785,36 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
       <c r="I3" s="1"/>
     </row>
     <row r="4" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
       <c r="I5" s="1"/>
     </row>
     <row r="7" spans="1:12" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -841,61 +844,61 @@
       <c r="L8" s="7"/>
     </row>
     <row r="9" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="10"/>
+      <c r="C9" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
     </row>
     <row r="10" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
     </row>
     <row r="11" spans="1:12" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="13"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="10"/>
       <c r="J11" s="6" t="s">
         <v>9</v>
       </c>
@@ -907,72 +910,75 @@
       </c>
     </row>
     <row r="34" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D37" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B43" s="8"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8"/>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
+      <c r="B43" s="16"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+      <c r="J43" s="16"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9" t="s">
+      <c r="C44" s="17"/>
+      <c r="D44" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="9"/>
-      <c r="H44" s="9"/>
-      <c r="I44" s="9" t="s">
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="J44" s="9"/>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="D38:H38"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="I9:I11"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="D43:H43"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="D44:H44"/>
     <mergeCell ref="J9:L10"/>
     <mergeCell ref="A9:B11"/>
     <mergeCell ref="A3:H5"/>
@@ -982,12 +988,11 @@
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="G9:G11"/>
     <mergeCell ref="H9:H11"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="D43:H43"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="D44:H44"/>
+    <mergeCell ref="D37:H37"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="I9:I11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
